--- a/artfynd/A 14261-2026 artfynd.xlsx
+++ b/artfynd/A 14261-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121289340</v>
+        <v>121289336</v>
       </c>
       <c r="B2" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tyftet Medbön, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315565</v>
+        <v>315601</v>
       </c>
       <c r="R2" t="n">
-        <v>6513217</v>
+        <v>6513226</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,19 +781,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121289336</v>
+        <v>121289339</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -815,21 +810,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tyftet Medbön, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315601</v>
+        <v>315578</v>
       </c>
       <c r="R3" t="n">
-        <v>6513226</v>
+        <v>6513222</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,50 +882,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121289339</v>
+        <v>124571169</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tyftet Medbön, Boh</t>
+          <t>Medbönsberget, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>315578</v>
+        <v>315548</v>
       </c>
       <c r="R4" t="n">
-        <v>6513222</v>
+        <v>6513191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,26 +972,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124571169</v>
+        <v>121289335</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,39 +995,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Medbönsberget, Boh</t>
+          <t>Tyftet Medbön, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>315548</v>
+        <v>315612</v>
       </c>
       <c r="R5" t="n">
-        <v>6513191</v>
+        <v>6513237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,12 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,15 +1069,120 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121289340</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tyftet Medbön, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>315565</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6513217</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14261-2026 artfynd.xlsx
+++ b/artfynd/A 14261-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121289336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121289339</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571169</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121289335</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,8 +1208,20 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121289340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>